--- a/04_DESIGN_TABLES/DesignTable_2504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC5"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,6 +1433,193 @@
       <c r="BC5" t="inlineStr">
         <is>
           <t>2504-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="n">
+        <v>37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>45 deg Male JIC Union Elbow, 1 5/16-12 JIC x 1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; legs / flats / bores: OMi WebsitePartsInfo2026 Items M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID (= Brennan TFA p.26, one source); JIC ends MS33656J | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(OMi Hex Flat (Y), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; each leg bore runs from its face to the axis crossing; Brennan 2504-08-08-FG STEP (re-measured 2026-10-02, tools/measure/forged.py): both JIC tips 0.980, hex arms end 0.323 (= M - the 2403 -08 JIC end length 0.657), A/F 0.750, corner puck radius 0.433 = the hex corner radius, bores 0.391 = this pattern; JIC seat / land / cone / thread major = the 2403 -08 chain, but the STEP shows NO thread relief (thread major runs to the hex face): the model keeps the MS33656J relief of the 2403 chain, as every built tee / elbow (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bores from OMi Items (= Brennan TFA p.26, one source) | hex A/F raised from OMi Hex Flat 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
         </is>
       </c>
     </row>
